--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,42 +1128,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R6" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1245,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R7" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,6 +1358,363 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129491644</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96158</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>210</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högströmskavägen nordöster, Högströmskavägen nordöster, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471257</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6543268</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129490981</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96158</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högströmskavägen nordöster, Högströmskavägen nordöster, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471232</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6543318</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>20 cm från granens stam, på kraftigt nedbruten förna, östra sidan av granen. Påmärkt m gult band</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129492527</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ågrenafallsvägen, Rankemossen L, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471303</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6543297</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett. På tall öster om vägen. Ca 3 m in från vägen. Ca 2,5 m upp. Syns tydligt i kikare. Men man kan se med blotta ögat. Märkt trädet med ett kort gult märkband.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96158</v>
+        <v>96166</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96158</v>
+        <v>96166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,38 +1128,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R6" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,42 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R7" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,42 +1128,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R6" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1245,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R7" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,38 +1128,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R6" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,42 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R7" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,42 +1128,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R6" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1245,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R7" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,38 +1128,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R6" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,42 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R7" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490876</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129491760</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129491248</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,38 +1128,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R6" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,42 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R7" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129492527</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490876</v>
       </c>
       <c r="B2" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129491760</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129491248</v>
       </c>
       <c r="B4" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129492527</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490876</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129491760</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129491248</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129492527</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,42 +1128,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B6" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R6" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1245,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>92875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R7" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,38 +1128,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>92875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R6" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,42 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R7" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,42 +1128,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B6" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R6" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1245,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>92879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R7" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>129490880</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,38 +1128,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>92881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R6" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,42 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B7" t="n">
-        <v>92879</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R7" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -1128,42 +1128,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129491012</v>
+        <v>129491220</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471212</v>
+        <v>471217</v>
       </c>
       <c r="R6" t="n">
-        <v>6543273</v>
+        <v>6543230</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1245,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129491220</v>
+        <v>129491012</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>92881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471217</v>
+        <v>471212</v>
       </c>
       <c r="R7" t="n">
-        <v>6543230</v>
+        <v>6543273</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
         <v>129491644</v>
       </c>
       <c r="B8" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129490981</v>
       </c>
       <c r="B9" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54303-2022 artfynd.xlsx
+++ b/artfynd/A 54303-2022 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>131253288</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>131253282</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
